--- a/src/main/resources/template2.xlsx
+++ b/src/main/resources/template2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20295" windowHeight="9750" activeTab="1"/>
+    <workbookView windowWidth="20385" windowHeight="8370" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="附注" sheetId="1" r:id="rId1"/>
@@ -1159,10 +1159,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="42">
     <font>
@@ -1208,13 +1208,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1247,6 +1247,27 @@
       <sz val="10.5"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1264,6 +1285,75 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -1279,51 +1369,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -1332,51 +1377,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -1394,7 +1394,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1478,19 +1478,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1502,13 +1514,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1526,19 +1544,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1550,37 +1634,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1598,67 +1652,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1851,6 +1851,21 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1875,21 +1890,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -1901,30 +1901,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1952,42 +1928,66 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1996,116 +1996,116 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2176,7 +2176,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2188,7 +2188,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2200,10 +2200,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2218,10 +2215,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2230,10 +2224,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2814,12 +2808,11 @@
       <a:lstStyle/>
     </a:spDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
@@ -2828,108 +2821,108 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.75" customHeight="1" spans="1:7">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
     </row>
     <row r="2" ht="33" customHeight="1" spans="1:1">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="63" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="33" customHeight="1" spans="1:1">
-      <c r="A3" s="66" t="s">
+      <c r="A3" s="64" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" ht="33" customHeight="1" spans="1:1">
-      <c r="A4" s="65" t="s">
+      <c r="A4" s="63" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" ht="33" customHeight="1" spans="1:1">
-      <c r="A5" s="66" t="s">
+      <c r="A5" s="64" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="33" customHeight="1" spans="1:1">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="65" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" ht="33" customHeight="1" spans="1:1">
-      <c r="A7" s="68" t="s">
+      <c r="A7" s="66" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" ht="33" customHeight="1" spans="1:1">
-      <c r="A8" s="68" t="s">
+      <c r="A8" s="66" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" ht="33" customHeight="1" spans="1:1">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="66" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" ht="33" customHeight="1" spans="1:1">
-      <c r="A10" s="68" t="s">
+      <c r="A10" s="66" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" ht="33" customHeight="1" spans="1:1">
-      <c r="A11" s="67" t="s">
+      <c r="A11" s="65" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" ht="33" customHeight="1" spans="1:1">
-      <c r="A12" s="69" t="s">
+      <c r="A12" s="67" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" ht="33" customHeight="1" spans="1:1">
-      <c r="A13" s="70" t="s">
+      <c r="A13" s="68" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" ht="33" customHeight="1" spans="1:1">
-      <c r="A14" s="68" t="s">
+      <c r="A14" s="66" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" ht="33" customHeight="1" spans="1:1">
-      <c r="A15" s="71" t="s">
+      <c r="A15" s="69" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" ht="33" customHeight="1" spans="1:1">
-      <c r="A16" s="72" t="s">
+      <c r="A16" s="70" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" ht="33" customHeight="1" spans="1:1">
-      <c r="A17" s="73" t="s">
+      <c r="A17" s="71" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" ht="33" customHeight="1" spans="1:1">
-      <c r="A18" s="74" t="s">
+      <c r="A18" s="72" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" ht="33" customHeight="1" spans="1:1">
-      <c r="A19" s="75" t="s">
+      <c r="A19" s="73" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="76"/>
+      <c r="A20" s="74"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2940,7 +2933,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
@@ -2976,7 +2969,7 @@
       <c r="H2" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="51"/>
+      <c r="I2" s="49"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:10">
       <c r="A3" s="16" t="s">
@@ -2989,8 +2982,8 @@
       <c r="F3" s="17"/>
       <c r="G3" s="17"/>
       <c r="H3" s="17"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="53"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:10">
       <c r="A4" s="18" t="s">
@@ -3018,7 +3011,7 @@
       <c r="I4" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="53"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:10">
       <c r="A5" s="21" t="s">
@@ -3044,7 +3037,7 @@
       <c r="I5" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="53"/>
+      <c r="J5" s="51"/>
     </row>
     <row r="6" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A6" s="23" t="s">
@@ -3067,10 +3060,10 @@
       <c r="H6" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="54" t="s">
+      <c r="I6" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="J6" s="55"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A7" s="23" t="s">
@@ -3096,7 +3089,7 @@
       <c r="I7" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="J7" s="55"/>
+      <c r="J7" s="53"/>
     </row>
     <row r="8" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A8" s="23" t="s">
@@ -3122,7 +3115,7 @@
       <c r="I8" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="J8" s="55"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A9" s="23" t="s">
@@ -3145,10 +3138,10 @@
       <c r="H9" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="56" t="s">
+      <c r="I9" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="J9" s="55"/>
+      <c r="J9" s="53"/>
     </row>
     <row r="10" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A10" s="23"/>
@@ -3160,7 +3153,7 @@
       <c r="G10" s="25"/>
       <c r="H10" s="18"/>
       <c r="I10" s="18"/>
-      <c r="J10" s="55"/>
+      <c r="J10" s="53"/>
     </row>
     <row r="11" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A11" s="23"/>
@@ -3172,7 +3165,7 @@
       <c r="G11" s="25"/>
       <c r="H11" s="18"/>
       <c r="I11" s="18"/>
-      <c r="J11" s="55"/>
+      <c r="J11" s="53"/>
     </row>
     <row r="12" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A12" s="27"/>
@@ -3184,7 +3177,7 @@
       <c r="G12" s="25"/>
       <c r="H12" s="18"/>
       <c r="I12" s="54"/>
-      <c r="J12" s="55"/>
+      <c r="J12" s="53"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A13" s="27"/>
@@ -3196,7 +3189,7 @@
       <c r="G13" s="25"/>
       <c r="H13" s="18"/>
       <c r="I13" s="18"/>
-      <c r="J13" s="55"/>
+      <c r="J13" s="53"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A14" s="27"/>
@@ -3208,7 +3201,7 @@
       <c r="G14" s="25"/>
       <c r="H14" s="18"/>
       <c r="I14" s="18"/>
-      <c r="J14" s="55"/>
+      <c r="J14" s="53"/>
     </row>
     <row r="15" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A15" s="27"/>
@@ -3220,7 +3213,7 @@
       <c r="G15" s="25"/>
       <c r="H15" s="18"/>
       <c r="I15" s="54"/>
-      <c r="J15" s="55"/>
+      <c r="J15" s="53"/>
     </row>
     <row r="16" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A16" s="27"/>
@@ -3232,7 +3225,7 @@
       <c r="G16" s="25"/>
       <c r="H16" s="18"/>
       <c r="I16" s="18"/>
-      <c r="J16" s="55"/>
+      <c r="J16" s="53"/>
     </row>
     <row r="17" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A17" s="27"/>
@@ -3244,7 +3237,7 @@
       <c r="G17" s="25"/>
       <c r="H17" s="18"/>
       <c r="I17" s="18"/>
-      <c r="J17" s="55"/>
+      <c r="J17" s="53"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A18" s="27"/>
@@ -3256,7 +3249,7 @@
       <c r="G18" s="25"/>
       <c r="H18" s="18"/>
       <c r="I18" s="18"/>
-      <c r="J18" s="55"/>
+      <c r="J18" s="53"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A19" s="27"/>
@@ -3268,7 +3261,7 @@
       <c r="G19" s="25"/>
       <c r="H19" s="18"/>
       <c r="I19" s="18"/>
-      <c r="J19" s="55"/>
+      <c r="J19" s="53"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A20" s="31"/>
@@ -3280,10 +3273,10 @@
       <c r="G20" s="25"/>
       <c r="H20" s="18"/>
       <c r="I20" s="18"/>
-      <c r="J20" s="55"/>
+      <c r="J20" s="53"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A21" s="32"/>
+      <c r="A21" s="21"/>
       <c r="B21" s="26"/>
       <c r="C21" s="24"/>
       <c r="D21" s="24"/>
@@ -3292,7 +3285,7 @@
       <c r="G21" s="25"/>
       <c r="H21" s="18"/>
       <c r="I21" s="18"/>
-      <c r="J21" s="55"/>
+      <c r="J21" s="53"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A22" s="23"/>
@@ -3304,10 +3297,10 @@
       <c r="G22" s="25"/>
       <c r="H22" s="18"/>
       <c r="I22" s="18"/>
-      <c r="J22" s="55"/>
+      <c r="J22" s="53"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A23" s="32"/>
+      <c r="A23" s="21"/>
       <c r="B23" s="28"/>
       <c r="C23" s="29"/>
       <c r="D23" s="30"/>
@@ -3316,7 +3309,7 @@
       <c r="G23" s="25"/>
       <c r="H23" s="18"/>
       <c r="I23" s="18"/>
-      <c r="J23" s="55"/>
+      <c r="J23" s="53"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A24" s="27"/>
@@ -3328,7 +3321,7 @@
       <c r="G24" s="25"/>
       <c r="H24" s="18"/>
       <c r="I24" s="18"/>
-      <c r="J24" s="55"/>
+      <c r="J24" s="53"/>
     </row>
     <row r="25" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A25" s="27"/>
@@ -3340,7 +3333,7 @@
       <c r="G25" s="25"/>
       <c r="H25" s="18"/>
       <c r="I25" s="18"/>
-      <c r="J25" s="55"/>
+      <c r="J25" s="53"/>
     </row>
     <row r="26" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A26" s="23"/>
@@ -3352,10 +3345,10 @@
       <c r="G26" s="25"/>
       <c r="H26" s="18"/>
       <c r="I26" s="18"/>
-      <c r="J26" s="55"/>
+      <c r="J26" s="53"/>
     </row>
     <row r="27" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A27" s="32"/>
+      <c r="A27" s="21"/>
       <c r="B27" s="26"/>
       <c r="C27" s="24"/>
       <c r="D27" s="24"/>
@@ -3364,21 +3357,21 @@
       <c r="G27" s="25"/>
       <c r="H27" s="18"/>
       <c r="I27" s="18"/>
-      <c r="J27" s="55"/>
+      <c r="J27" s="53"/>
     </row>
     <row r="28" s="2" customFormat="1" ht="30" customHeight="1" spans="1:10">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="55"/>
+      <c r="B28" s="33"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="53"/>
     </row>
     <row r="29" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A29" s="23" t="s">
@@ -3390,11 +3383,11 @@
       <c r="C29" s="24"/>
       <c r="D29" s="24"/>
       <c r="E29" s="18"/>
-      <c r="F29" s="35"/>
+      <c r="F29" s="34"/>
       <c r="G29" s="25"/>
       <c r="H29" s="18"/>
       <c r="I29" s="18"/>
-      <c r="J29" s="55"/>
+      <c r="J29" s="53"/>
     </row>
     <row r="30" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A30" s="23" t="s">
@@ -3406,119 +3399,119 @@
       <c r="C30" s="24"/>
       <c r="D30" s="24"/>
       <c r="E30" s="18"/>
-      <c r="F30" s="36"/>
+      <c r="F30" s="35"/>
       <c r="G30" s="25"/>
       <c r="H30" s="18"/>
       <c r="I30" s="18"/>
-      <c r="J30" s="55"/>
+      <c r="J30" s="53"/>
     </row>
     <row r="31" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A31" s="37"/>
+      <c r="A31" s="36"/>
       <c r="B31" s="26"/>
       <c r="C31" s="24"/>
       <c r="D31" s="24"/>
       <c r="E31" s="18"/>
-      <c r="F31" s="36"/>
+      <c r="F31" s="35"/>
       <c r="G31" s="25"/>
       <c r="H31" s="18"/>
       <c r="I31" s="18"/>
-      <c r="J31" s="55"/>
+      <c r="J31" s="53"/>
     </row>
     <row r="32" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A32" s="38"/>
-      <c r="B32" s="39"/>
+      <c r="A32" s="34"/>
+      <c r="B32" s="37"/>
       <c r="C32" s="29"/>
       <c r="D32" s="30"/>
       <c r="E32" s="18"/>
-      <c r="F32" s="40"/>
+      <c r="F32" s="38"/>
       <c r="G32" s="25"/>
       <c r="H32" s="18"/>
       <c r="I32" s="18"/>
-      <c r="J32" s="55"/>
+      <c r="J32" s="53"/>
     </row>
     <row r="33" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A33" s="41"/>
+      <c r="A33" s="39"/>
       <c r="B33" s="26"/>
       <c r="C33" s="24"/>
       <c r="D33" s="24"/>
       <c r="E33" s="18"/>
-      <c r="F33" s="40"/>
+      <c r="F33" s="38"/>
       <c r="G33" s="25"/>
       <c r="H33" s="18"/>
       <c r="I33" s="18"/>
-      <c r="J33" s="55"/>
+      <c r="J33" s="53"/>
     </row>
     <row r="34" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A34" s="41"/>
+      <c r="A34" s="39"/>
       <c r="B34" s="26"/>
       <c r="C34" s="24"/>
       <c r="D34" s="24"/>
       <c r="E34" s="18"/>
-      <c r="F34" s="40"/>
+      <c r="F34" s="38"/>
       <c r="G34" s="25"/>
       <c r="H34" s="18"/>
       <c r="I34" s="18"/>
-      <c r="J34" s="55"/>
+      <c r="J34" s="53"/>
     </row>
     <row r="35" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A35" s="42"/>
+      <c r="A35" s="40"/>
       <c r="B35" s="26"/>
       <c r="C35" s="24"/>
       <c r="D35" s="24"/>
       <c r="E35" s="18"/>
-      <c r="F35" s="40"/>
+      <c r="F35" s="38"/>
       <c r="G35" s="25"/>
       <c r="H35" s="18"/>
       <c r="I35" s="18"/>
-      <c r="J35" s="55"/>
+      <c r="J35" s="53"/>
     </row>
     <row r="36" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A36" s="37"/>
+      <c r="A36" s="36"/>
       <c r="B36" s="26"/>
       <c r="C36" s="24"/>
       <c r="D36" s="24"/>
       <c r="E36" s="18"/>
-      <c r="F36" s="40"/>
+      <c r="F36" s="38"/>
       <c r="G36" s="25"/>
       <c r="H36" s="18"/>
       <c r="I36" s="18"/>
-      <c r="J36" s="55"/>
+      <c r="J36" s="53"/>
     </row>
     <row r="37" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A37" s="37"/>
+      <c r="A37" s="36"/>
       <c r="B37" s="26"/>
       <c r="C37" s="24"/>
       <c r="D37" s="24"/>
       <c r="E37" s="18"/>
-      <c r="F37" s="40"/>
+      <c r="F37" s="38"/>
       <c r="G37" s="25"/>
       <c r="H37" s="18"/>
       <c r="I37" s="18"/>
-      <c r="J37" s="55"/>
+      <c r="J37" s="53"/>
     </row>
     <row r="38" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A38" s="37"/>
+      <c r="A38" s="36"/>
       <c r="B38" s="26"/>
       <c r="C38" s="24"/>
       <c r="D38" s="24"/>
       <c r="E38" s="18"/>
-      <c r="F38" s="40"/>
+      <c r="F38" s="38"/>
       <c r="G38" s="25"/>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
-      <c r="J38" s="55"/>
+      <c r="J38" s="53"/>
     </row>
     <row r="39" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A39" s="37"/>
+      <c r="A39" s="36"/>
       <c r="B39" s="26"/>
       <c r="C39" s="24"/>
       <c r="D39" s="24"/>
       <c r="E39" s="18"/>
-      <c r="F39" s="40"/>
+      <c r="F39" s="38"/>
       <c r="G39" s="25"/>
       <c r="H39" s="18"/>
       <c r="I39" s="18"/>
-      <c r="J39" s="55"/>
+      <c r="J39" s="53"/>
     </row>
     <row r="40" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
       <c r="A40" s="16" t="s">
@@ -3531,127 +3524,127 @@
       <c r="F40" s="17"/>
       <c r="G40" s="17"/>
       <c r="H40" s="17"/>
-      <c r="I40" s="52"/>
+      <c r="I40" s="50"/>
     </row>
     <row r="41" s="1" customFormat="1" ht="50.1" customHeight="1" spans="1:9">
-      <c r="A41" s="43"/>
-      <c r="B41" s="44"/>
-      <c r="C41" s="44"/>
-      <c r="D41" s="44"/>
-      <c r="E41" s="44"/>
-      <c r="F41" s="44"/>
-      <c r="G41" s="44"/>
-      <c r="H41" s="44"/>
-      <c r="I41" s="58"/>
+      <c r="A41" s="41"/>
+      <c r="B41" s="42"/>
+      <c r="C41" s="42"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="42"/>
+      <c r="H41" s="42"/>
+      <c r="I41" s="56"/>
     </row>
     <row r="42" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A42" s="33" t="s">
+      <c r="A42" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="B42" s="34"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="34"/>
-      <c r="G42" s="34"/>
-      <c r="H42" s="34"/>
-      <c r="I42" s="57"/>
+      <c r="B42" s="33"/>
+      <c r="C42" s="33"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="33"/>
+      <c r="F42" s="33"/>
+      <c r="G42" s="33"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="55"/>
     </row>
     <row r="43" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A43" s="40" t="s">
+      <c r="A43" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="45"/>
-      <c r="C43" s="46"/>
-      <c r="D43" s="46"/>
-      <c r="E43" s="46"/>
-      <c r="F43" s="46"/>
-      <c r="G43" s="46"/>
-      <c r="H43" s="46"/>
-      <c r="I43" s="59"/>
+      <c r="B43" s="43"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="57"/>
     </row>
     <row r="44" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A44" s="40" t="s">
+      <c r="A44" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="B44" s="45"/>
-      <c r="C44" s="46"/>
-      <c r="D44" s="46"/>
-      <c r="E44" s="46"/>
-      <c r="F44" s="46"/>
-      <c r="G44" s="46"/>
-      <c r="H44" s="46"/>
-      <c r="I44" s="59"/>
+      <c r="B44" s="43"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="44"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="44"/>
+      <c r="I44" s="57"/>
     </row>
     <row r="45" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A45" s="40" t="s">
+      <c r="A45" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="B45" s="45"/>
-      <c r="C45" s="46"/>
-      <c r="D45" s="46"/>
-      <c r="E45" s="46"/>
-      <c r="F45" s="46"/>
-      <c r="G45" s="46"/>
-      <c r="H45" s="46"/>
-      <c r="I45" s="59"/>
+      <c r="B45" s="43"/>
+      <c r="C45" s="44"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="44"/>
+      <c r="F45" s="44"/>
+      <c r="G45" s="44"/>
+      <c r="H45" s="44"/>
+      <c r="I45" s="57"/>
     </row>
     <row r="46" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A46" s="47" t="s">
+      <c r="A46" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="B46" s="47"/>
-      <c r="C46" s="47"/>
-      <c r="D46" s="47"/>
-      <c r="E46" s="47"/>
-      <c r="F46" s="47"/>
-      <c r="G46" s="47"/>
-      <c r="H46" s="47"/>
-      <c r="I46" s="60"/>
+      <c r="B46" s="45"/>
+      <c r="C46" s="45"/>
+      <c r="D46" s="45"/>
+      <c r="E46" s="45"/>
+      <c r="F46" s="45"/>
+      <c r="G46" s="45"/>
+      <c r="H46" s="45"/>
+      <c r="I46" s="58"/>
     </row>
     <row r="47" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A47" s="48"/>
-      <c r="B47" s="48"/>
-      <c r="C47" s="48"/>
-      <c r="D47" s="48"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="48"/>
-      <c r="G47" s="48"/>
-      <c r="H47" s="48"/>
-      <c r="I47" s="61"/>
+      <c r="A47" s="46"/>
+      <c r="B47" s="46"/>
+      <c r="C47" s="46"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="46"/>
+      <c r="G47" s="46"/>
+      <c r="H47" s="46"/>
+      <c r="I47" s="59"/>
     </row>
     <row r="48" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A48" s="48"/>
-      <c r="B48" s="48"/>
-      <c r="C48" s="48"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="48"/>
-      <c r="G48" s="48"/>
-      <c r="H48" s="48"/>
-      <c r="I48" s="61"/>
+      <c r="A48" s="46"/>
+      <c r="B48" s="46"/>
+      <c r="C48" s="46"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="46"/>
+      <c r="F48" s="46"/>
+      <c r="G48" s="46"/>
+      <c r="H48" s="46"/>
+      <c r="I48" s="59"/>
     </row>
     <row r="49" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A49" s="48"/>
-      <c r="B49" s="48"/>
-      <c r="C49" s="48"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="48"/>
-      <c r="I49" s="61"/>
+      <c r="A49" s="46"/>
+      <c r="B49" s="46"/>
+      <c r="C49" s="46"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="46"/>
+      <c r="G49" s="46"/>
+      <c r="H49" s="46"/>
+      <c r="I49" s="59"/>
     </row>
     <row r="50" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A50" s="49"/>
-      <c r="B50" s="50"/>
-      <c r="C50" s="50"/>
-      <c r="D50" s="50"/>
-      <c r="E50" s="50"/>
-      <c r="F50" s="50"/>
-      <c r="G50" s="50"/>
-      <c r="H50" s="50"/>
-      <c r="I50" s="62"/>
+      <c r="A50" s="47"/>
+      <c r="B50" s="48"/>
+      <c r="C50" s="48"/>
+      <c r="D50" s="48"/>
+      <c r="E50" s="48"/>
+      <c r="F50" s="48"/>
+      <c r="G50" s="48"/>
+      <c r="H50" s="48"/>
+      <c r="I50" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="51">

--- a/src/main/resources/template2.xlsx
+++ b/src/main/resources/template2.xlsx
@@ -1250,9 +1250,53 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1263,15 +1307,72 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1286,115 +1387,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1478,13 +1478,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1502,163 +1658,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1851,6 +1851,30 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1872,11 +1896,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1884,23 +1906,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1922,33 +1944,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1957,155 +1957,155 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2228,6 +2228,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2821,108 +2830,108 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.75" customHeight="1" spans="1:7">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
     </row>
     <row r="2" ht="33" customHeight="1" spans="1:1">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="66" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="33" customHeight="1" spans="1:1">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="67" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" ht="33" customHeight="1" spans="1:1">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="66" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" ht="33" customHeight="1" spans="1:1">
-      <c r="A5" s="64" t="s">
+      <c r="A5" s="67" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="33" customHeight="1" spans="1:1">
-      <c r="A6" s="65" t="s">
+      <c r="A6" s="68" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" ht="33" customHeight="1" spans="1:1">
-      <c r="A7" s="66" t="s">
+      <c r="A7" s="69" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" ht="33" customHeight="1" spans="1:1">
-      <c r="A8" s="66" t="s">
+      <c r="A8" s="69" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" ht="33" customHeight="1" spans="1:1">
-      <c r="A9" s="66" t="s">
+      <c r="A9" s="69" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" ht="33" customHeight="1" spans="1:1">
-      <c r="A10" s="66" t="s">
+      <c r="A10" s="69" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" ht="33" customHeight="1" spans="1:1">
-      <c r="A11" s="65" t="s">
+      <c r="A11" s="68" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" ht="33" customHeight="1" spans="1:1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="70" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" ht="33" customHeight="1" spans="1:1">
-      <c r="A13" s="68" t="s">
+      <c r="A13" s="71" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" ht="33" customHeight="1" spans="1:1">
-      <c r="A14" s="66" t="s">
+      <c r="A14" s="69" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" ht="33" customHeight="1" spans="1:1">
-      <c r="A15" s="69" t="s">
+      <c r="A15" s="72" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" ht="33" customHeight="1" spans="1:1">
-      <c r="A16" s="70" t="s">
+      <c r="A16" s="73" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" ht="33" customHeight="1" spans="1:1">
-      <c r="A17" s="71" t="s">
+      <c r="A17" s="74" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" ht="33" customHeight="1" spans="1:1">
-      <c r="A18" s="72" t="s">
+      <c r="A18" s="75" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" ht="33" customHeight="1" spans="1:1">
-      <c r="A19" s="73" t="s">
+      <c r="A19" s="76" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="74"/>
+      <c r="A20" s="77"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2935,7 +2944,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.2916666666667" style="3" customWidth="1"/>
@@ -2969,7 +2978,7 @@
       <c r="H2" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="49"/>
+      <c r="I2" s="52"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:10">
       <c r="A3" s="16" t="s">
@@ -2982,8 +2991,8 @@
       <c r="F3" s="17"/>
       <c r="G3" s="17"/>
       <c r="H3" s="17"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="51"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="54"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:10">
       <c r="A4" s="18" t="s">
@@ -3011,7 +3020,7 @@
       <c r="I4" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="51"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:10">
       <c r="A5" s="21" t="s">
@@ -3037,7 +3046,7 @@
       <c r="I5" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="51"/>
+      <c r="J5" s="54"/>
     </row>
     <row r="6" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A6" s="23" t="s">
@@ -3060,10 +3069,10 @@
       <c r="H6" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="52" t="s">
+      <c r="I6" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="J6" s="53"/>
+      <c r="J6" s="56"/>
     </row>
     <row r="7" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A7" s="23" t="s">
@@ -3089,7 +3098,7 @@
       <c r="I7" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="J7" s="53"/>
+      <c r="J7" s="56"/>
     </row>
     <row r="8" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A8" s="23" t="s">
@@ -3115,7 +3124,7 @@
       <c r="I8" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="J8" s="53"/>
+      <c r="J8" s="56"/>
     </row>
     <row r="9" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A9" s="23" t="s">
@@ -3138,10 +3147,10 @@
       <c r="H9" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="52" t="s">
+      <c r="I9" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="J9" s="53"/>
+      <c r="J9" s="56"/>
     </row>
     <row r="10" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A10" s="23"/>
@@ -3153,7 +3162,7 @@
       <c r="G10" s="25"/>
       <c r="H10" s="18"/>
       <c r="I10" s="18"/>
-      <c r="J10" s="53"/>
+      <c r="J10" s="56"/>
     </row>
     <row r="11" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A11" s="23"/>
@@ -3165,7 +3174,7 @@
       <c r="G11" s="25"/>
       <c r="H11" s="18"/>
       <c r="I11" s="18"/>
-      <c r="J11" s="53"/>
+      <c r="J11" s="56"/>
     </row>
     <row r="12" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A12" s="27"/>
@@ -3176,8 +3185,8 @@
       <c r="F12" s="18"/>
       <c r="G12" s="25"/>
       <c r="H12" s="18"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="53"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="56"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A13" s="27"/>
@@ -3189,7 +3198,7 @@
       <c r="G13" s="25"/>
       <c r="H13" s="18"/>
       <c r="I13" s="18"/>
-      <c r="J13" s="53"/>
+      <c r="J13" s="56"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A14" s="27"/>
@@ -3201,7 +3210,7 @@
       <c r="G14" s="25"/>
       <c r="H14" s="18"/>
       <c r="I14" s="18"/>
-      <c r="J14" s="53"/>
+      <c r="J14" s="56"/>
     </row>
     <row r="15" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A15" s="27"/>
@@ -3212,8 +3221,8 @@
       <c r="F15" s="18"/>
       <c r="G15" s="25"/>
       <c r="H15" s="18"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="53"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="56"/>
     </row>
     <row r="16" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A16" s="27"/>
@@ -3225,7 +3234,7 @@
       <c r="G16" s="25"/>
       <c r="H16" s="18"/>
       <c r="I16" s="18"/>
-      <c r="J16" s="53"/>
+      <c r="J16" s="56"/>
     </row>
     <row r="17" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A17" s="27"/>
@@ -3237,7 +3246,7 @@
       <c r="G17" s="25"/>
       <c r="H17" s="18"/>
       <c r="I17" s="18"/>
-      <c r="J17" s="53"/>
+      <c r="J17" s="56"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A18" s="27"/>
@@ -3249,7 +3258,7 @@
       <c r="G18" s="25"/>
       <c r="H18" s="18"/>
       <c r="I18" s="18"/>
-      <c r="J18" s="53"/>
+      <c r="J18" s="56"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A19" s="27"/>
@@ -3261,7 +3270,7 @@
       <c r="G19" s="25"/>
       <c r="H19" s="18"/>
       <c r="I19" s="18"/>
-      <c r="J19" s="53"/>
+      <c r="J19" s="56"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A20" s="31"/>
@@ -3273,7 +3282,7 @@
       <c r="G20" s="25"/>
       <c r="H20" s="18"/>
       <c r="I20" s="18"/>
-      <c r="J20" s="53"/>
+      <c r="J20" s="56"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A21" s="21"/>
@@ -3285,7 +3294,7 @@
       <c r="G21" s="25"/>
       <c r="H21" s="18"/>
       <c r="I21" s="18"/>
-      <c r="J21" s="53"/>
+      <c r="J21" s="56"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A22" s="23"/>
@@ -3297,7 +3306,7 @@
       <c r="G22" s="25"/>
       <c r="H22" s="18"/>
       <c r="I22" s="18"/>
-      <c r="J22" s="53"/>
+      <c r="J22" s="56"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A23" s="21"/>
@@ -3309,7 +3318,7 @@
       <c r="G23" s="25"/>
       <c r="H23" s="18"/>
       <c r="I23" s="18"/>
-      <c r="J23" s="53"/>
+      <c r="J23" s="56"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A24" s="27"/>
@@ -3321,7 +3330,7 @@
       <c r="G24" s="25"/>
       <c r="H24" s="18"/>
       <c r="I24" s="18"/>
-      <c r="J24" s="53"/>
+      <c r="J24" s="56"/>
     </row>
     <row r="25" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A25" s="27"/>
@@ -3333,7 +3342,7 @@
       <c r="G25" s="25"/>
       <c r="H25" s="18"/>
       <c r="I25" s="18"/>
-      <c r="J25" s="53"/>
+      <c r="J25" s="56"/>
     </row>
     <row r="26" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A26" s="23"/>
@@ -3345,7 +3354,7 @@
       <c r="G26" s="25"/>
       <c r="H26" s="18"/>
       <c r="I26" s="18"/>
-      <c r="J26" s="53"/>
+      <c r="J26" s="56"/>
     </row>
     <row r="27" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A27" s="21"/>
@@ -3357,7 +3366,7 @@
       <c r="G27" s="25"/>
       <c r="H27" s="18"/>
       <c r="I27" s="18"/>
-      <c r="J27" s="53"/>
+      <c r="J27" s="56"/>
     </row>
     <row r="28" s="2" customFormat="1" ht="30" customHeight="1" spans="1:10">
       <c r="A28" s="32" t="s">
@@ -3370,8 +3379,8 @@
       <c r="F28" s="33"/>
       <c r="G28" s="33"/>
       <c r="H28" s="33"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="53"/>
+      <c r="I28" s="58"/>
+      <c r="J28" s="56"/>
     </row>
     <row r="29" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A29" s="23" t="s">
@@ -3387,7 +3396,7 @@
       <c r="G29" s="25"/>
       <c r="H29" s="18"/>
       <c r="I29" s="18"/>
-      <c r="J29" s="53"/>
+      <c r="J29" s="56"/>
     </row>
     <row r="30" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A30" s="23" t="s">
@@ -3403,7 +3412,7 @@
       <c r="G30" s="25"/>
       <c r="H30" s="18"/>
       <c r="I30" s="18"/>
-      <c r="J30" s="53"/>
+      <c r="J30" s="56"/>
     </row>
     <row r="31" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A31" s="36"/>
@@ -3415,7 +3424,7 @@
       <c r="G31" s="25"/>
       <c r="H31" s="18"/>
       <c r="I31" s="18"/>
-      <c r="J31" s="53"/>
+      <c r="J31" s="56"/>
     </row>
     <row r="32" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A32" s="34"/>
@@ -3427,7 +3436,7 @@
       <c r="G32" s="25"/>
       <c r="H32" s="18"/>
       <c r="I32" s="18"/>
-      <c r="J32" s="53"/>
+      <c r="J32" s="56"/>
     </row>
     <row r="33" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A33" s="39"/>
@@ -3439,7 +3448,7 @@
       <c r="G33" s="25"/>
       <c r="H33" s="18"/>
       <c r="I33" s="18"/>
-      <c r="J33" s="53"/>
+      <c r="J33" s="56"/>
     </row>
     <row r="34" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A34" s="39"/>
@@ -3451,7 +3460,7 @@
       <c r="G34" s="25"/>
       <c r="H34" s="18"/>
       <c r="I34" s="18"/>
-      <c r="J34" s="53"/>
+      <c r="J34" s="56"/>
     </row>
     <row r="35" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A35" s="40"/>
@@ -3463,7 +3472,7 @@
       <c r="G35" s="25"/>
       <c r="H35" s="18"/>
       <c r="I35" s="18"/>
-      <c r="J35" s="53"/>
+      <c r="J35" s="56"/>
     </row>
     <row r="36" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A36" s="36"/>
@@ -3475,7 +3484,7 @@
       <c r="G36" s="25"/>
       <c r="H36" s="18"/>
       <c r="I36" s="18"/>
-      <c r="J36" s="53"/>
+      <c r="J36" s="56"/>
     </row>
     <row r="37" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A37" s="36"/>
@@ -3487,7 +3496,7 @@
       <c r="G37" s="25"/>
       <c r="H37" s="18"/>
       <c r="I37" s="18"/>
-      <c r="J37" s="53"/>
+      <c r="J37" s="56"/>
     </row>
     <row r="38" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A38" s="36"/>
@@ -3499,155 +3508,167 @@
       <c r="G38" s="25"/>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
-      <c r="J38" s="53"/>
+      <c r="J38" s="56"/>
     </row>
     <row r="39" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A39" s="36"/>
-      <c r="B39" s="26"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
+      <c r="B39" s="41"/>
+      <c r="C39" s="42"/>
+      <c r="D39" s="43"/>
       <c r="E39" s="18"/>
       <c r="F39" s="38"/>
       <c r="G39" s="25"/>
       <c r="H39" s="18"/>
       <c r="I39" s="18"/>
-      <c r="J39" s="53"/>
-    </row>
-    <row r="40" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A40" s="16" t="s">
+      <c r="J39" s="56"/>
+    </row>
+    <row r="40" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
+      <c r="A40" s="36"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="56"/>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
+      <c r="A41" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="50"/>
-    </row>
-    <row r="41" s="1" customFormat="1" ht="50.1" customHeight="1" spans="1:9">
-      <c r="A41" s="41"/>
-      <c r="B41" s="42"/>
-      <c r="C41" s="42"/>
-      <c r="D41" s="42"/>
-      <c r="E41" s="42"/>
-      <c r="F41" s="42"/>
-      <c r="G41" s="42"/>
-      <c r="H41" s="42"/>
-      <c r="I41" s="56"/>
-    </row>
-    <row r="42" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A42" s="32" t="s">
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="53"/>
+    </row>
+    <row r="42" s="1" customFormat="1" ht="50.1" customHeight="1" spans="1:9">
+      <c r="A42" s="44"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="45"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="45"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="45"/>
+      <c r="I42" s="59"/>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
+      <c r="A43" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="B42" s="33"/>
-      <c r="C42" s="33"/>
-      <c r="D42" s="33"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="33"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="55"/>
-    </row>
-    <row r="43" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A43" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="B43" s="43"/>
-      <c r="C43" s="44"/>
-      <c r="D43" s="44"/>
-      <c r="E43" s="44"/>
-      <c r="F43" s="44"/>
-      <c r="G43" s="44"/>
-      <c r="H43" s="44"/>
-      <c r="I43" s="57"/>
+      <c r="B43" s="33"/>
+      <c r="C43" s="33"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="33"/>
+      <c r="F43" s="33"/>
+      <c r="G43" s="33"/>
+      <c r="H43" s="33"/>
+      <c r="I43" s="58"/>
     </row>
     <row r="44" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
       <c r="A44" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="B44" s="43"/>
-      <c r="C44" s="44"/>
-      <c r="D44" s="44"/>
-      <c r="E44" s="44"/>
-      <c r="F44" s="44"/>
-      <c r="G44" s="44"/>
-      <c r="H44" s="44"/>
-      <c r="I44" s="57"/>
+        <v>53</v>
+      </c>
+      <c r="B44" s="46"/>
+      <c r="C44" s="47"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="47"/>
+      <c r="G44" s="47"/>
+      <c r="H44" s="47"/>
+      <c r="I44" s="60"/>
     </row>
     <row r="45" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
       <c r="A45" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="B45" s="46"/>
+      <c r="C45" s="47"/>
+      <c r="D45" s="47"/>
+      <c r="E45" s="47"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="47"/>
+      <c r="H45" s="47"/>
+      <c r="I45" s="60"/>
+    </row>
+    <row r="46" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
+      <c r="A46" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="B45" s="43"/>
-      <c r="C45" s="44"/>
-      <c r="D45" s="44"/>
-      <c r="E45" s="44"/>
-      <c r="F45" s="44"/>
-      <c r="G45" s="44"/>
-      <c r="H45" s="44"/>
-      <c r="I45" s="57"/>
-    </row>
-    <row r="46" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A46" s="45" t="s">
+      <c r="B46" s="46"/>
+      <c r="C46" s="47"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="47"/>
+      <c r="F46" s="47"/>
+      <c r="G46" s="47"/>
+      <c r="H46" s="47"/>
+      <c r="I46" s="60"/>
+    </row>
+    <row r="47" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
+      <c r="A47" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="B46" s="45"/>
-      <c r="C46" s="45"/>
-      <c r="D46" s="45"/>
-      <c r="E46" s="45"/>
-      <c r="F46" s="45"/>
-      <c r="G46" s="45"/>
-      <c r="H46" s="45"/>
-      <c r="I46" s="58"/>
-    </row>
-    <row r="47" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A47" s="46"/>
-      <c r="B47" s="46"/>
-      <c r="C47" s="46"/>
-      <c r="D47" s="46"/>
-      <c r="E47" s="46"/>
-      <c r="F47" s="46"/>
-      <c r="G47" s="46"/>
-      <c r="H47" s="46"/>
-      <c r="I47" s="59"/>
+      <c r="B47" s="48"/>
+      <c r="C47" s="48"/>
+      <c r="D47" s="48"/>
+      <c r="E47" s="48"/>
+      <c r="F47" s="48"/>
+      <c r="G47" s="48"/>
+      <c r="H47" s="48"/>
+      <c r="I47" s="61"/>
     </row>
     <row r="48" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A48" s="46"/>
-      <c r="B48" s="46"/>
-      <c r="C48" s="46"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="46"/>
-      <c r="F48" s="46"/>
-      <c r="G48" s="46"/>
-      <c r="H48" s="46"/>
-      <c r="I48" s="59"/>
+      <c r="A48" s="49"/>
+      <c r="B48" s="49"/>
+      <c r="C48" s="49"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="49"/>
+      <c r="G48" s="49"/>
+      <c r="H48" s="49"/>
+      <c r="I48" s="62"/>
     </row>
     <row r="49" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A49" s="46"/>
-      <c r="B49" s="46"/>
-      <c r="C49" s="46"/>
-      <c r="D49" s="46"/>
-      <c r="E49" s="46"/>
-      <c r="F49" s="46"/>
-      <c r="G49" s="46"/>
-      <c r="H49" s="46"/>
-      <c r="I49" s="59"/>
+      <c r="A49" s="49"/>
+      <c r="B49" s="49"/>
+      <c r="C49" s="49"/>
+      <c r="D49" s="49"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="49"/>
+      <c r="G49" s="49"/>
+      <c r="H49" s="49"/>
+      <c r="I49" s="62"/>
     </row>
     <row r="50" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A50" s="47"/>
-      <c r="B50" s="48"/>
-      <c r="C50" s="48"/>
-      <c r="D50" s="48"/>
-      <c r="E50" s="48"/>
-      <c r="F50" s="48"/>
-      <c r="G50" s="48"/>
-      <c r="H50" s="48"/>
-      <c r="I50" s="60"/>
+      <c r="A50" s="49"/>
+      <c r="B50" s="49"/>
+      <c r="C50" s="49"/>
+      <c r="D50" s="49"/>
+      <c r="E50" s="49"/>
+      <c r="F50" s="49"/>
+      <c r="G50" s="49"/>
+      <c r="H50" s="49"/>
+      <c r="I50" s="62"/>
+    </row>
+    <row r="51" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
+      <c r="A51" s="50"/>
+      <c r="B51" s="51"/>
+      <c r="C51" s="51"/>
+      <c r="D51" s="51"/>
+      <c r="E51" s="51"/>
+      <c r="F51" s="51"/>
+      <c r="G51" s="51"/>
+      <c r="H51" s="51"/>
+      <c r="I51" s="63"/>
     </row>
   </sheetData>
-  <mergeCells count="51">
+  <mergeCells count="52">
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="H2:I2"/>
@@ -3688,17 +3709,18 @@
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B39:D39"/>
-    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="B40:D40"/>
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="A42:I42"/>
-    <mergeCell ref="B43:I43"/>
+    <mergeCell ref="A43:I43"/>
     <mergeCell ref="B44:I44"/>
     <mergeCell ref="B45:I45"/>
-    <mergeCell ref="A46:I46"/>
+    <mergeCell ref="B46:I46"/>
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="A48:I48"/>
     <mergeCell ref="A49:I49"/>
     <mergeCell ref="A50:I50"/>
+    <mergeCell ref="A51:I51"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.338888888888889" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="300"/>

--- a/src/main/resources/template2.xlsx
+++ b/src/main/resources/template2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20385" windowHeight="8370" activeTab="1"/>
+    <workbookView windowWidth="25395" windowHeight="11385" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="附注" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44">
   <si>
     <t xml:space="preserve">                                                                                                                                                          </t>
   </si>
@@ -1094,46 +1094,7 @@
     <t>完成情况</t>
   </si>
   <si>
-    <t>功能开发/后台组</t>
-  </si>
-  <si>
-    <t>配合测试同事测试智宝付自动轮询;</t>
-  </si>
-  <si>
-    <t>中</t>
-  </si>
-  <si>
-    <t>只有调账功能还不通</t>
-  </si>
-  <si>
-    <t>商家后台修改显示默认搜索条件</t>
-  </si>
-  <si>
-    <t>80&amp;</t>
-  </si>
-  <si>
-    <t>代码已写完,差测试</t>
-  </si>
-  <si>
-    <t>支付随机立减编写说明文档</t>
-  </si>
-  <si>
-    <t>修改相应的设计文档</t>
-  </si>
-  <si>
-    <t>客户要求调账,添加得宝管理员账户调账权限</t>
-  </si>
-  <si>
-    <t>已完成</t>
-  </si>
-  <si>
     <t>下周工作计划</t>
-  </si>
-  <si>
-    <t>支付汇--华势--京东扫码、qq扫码、代付</t>
-  </si>
-  <si>
-    <t>总后台网关通道ID 自增长</t>
   </si>
   <si>
     <t>余留问题</t>
@@ -1159,10 +1120,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="42">
     <font>
@@ -1249,6 +1210,22 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
@@ -1258,6 +1235,30 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1271,50 +1272,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -1323,6 +1280,56 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -1331,37 +1338,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -1370,9 +1346,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1381,20 +1356,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1478,13 +1439,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1502,7 +1481,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1514,7 +1595,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1526,139 +1619,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1851,6 +1812,45 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1874,7 +1874,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1897,47 +1897,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1957,155 +1918,155 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2228,15 +2189,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2817,11 +2769,12 @@
       <a:lstStyle/>
     </a:spDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
@@ -2830,108 +2783,108 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.75" customHeight="1" spans="1:7">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
     </row>
     <row r="2" ht="33" customHeight="1" spans="1:1">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="63" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="33" customHeight="1" spans="1:1">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="64" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" ht="33" customHeight="1" spans="1:1">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="63" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" ht="33" customHeight="1" spans="1:1">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="64" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="33" customHeight="1" spans="1:1">
-      <c r="A6" s="68" t="s">
+      <c r="A6" s="65" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" ht="33" customHeight="1" spans="1:1">
-      <c r="A7" s="69" t="s">
+      <c r="A7" s="66" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" ht="33" customHeight="1" spans="1:1">
-      <c r="A8" s="69" t="s">
+      <c r="A8" s="66" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" ht="33" customHeight="1" spans="1:1">
-      <c r="A9" s="69" t="s">
+      <c r="A9" s="66" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" ht="33" customHeight="1" spans="1:1">
-      <c r="A10" s="69" t="s">
+      <c r="A10" s="66" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" ht="33" customHeight="1" spans="1:1">
-      <c r="A11" s="68" t="s">
+      <c r="A11" s="65" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" ht="33" customHeight="1" spans="1:1">
-      <c r="A12" s="70" t="s">
+      <c r="A12" s="67" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" ht="33" customHeight="1" spans="1:1">
-      <c r="A13" s="71" t="s">
+      <c r="A13" s="68" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" ht="33" customHeight="1" spans="1:1">
-      <c r="A14" s="69" t="s">
+      <c r="A14" s="66" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" ht="33" customHeight="1" spans="1:1">
-      <c r="A15" s="72" t="s">
+      <c r="A15" s="69" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" ht="33" customHeight="1" spans="1:1">
-      <c r="A16" s="73" t="s">
+      <c r="A16" s="70" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" ht="33" customHeight="1" spans="1:1">
-      <c r="A17" s="74" t="s">
+      <c r="A17" s="71" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" ht="33" customHeight="1" spans="1:1">
-      <c r="A18" s="75" t="s">
+      <c r="A18" s="72" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" ht="33" customHeight="1" spans="1:1">
-      <c r="A19" s="76" t="s">
+      <c r="A19" s="73" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="77"/>
+      <c r="A20" s="74"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2942,7 +2895,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="A1:J51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
@@ -2978,7 +2931,7 @@
       <c r="H2" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="52"/>
+      <c r="I2" s="49"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:10">
       <c r="A3" s="16" t="s">
@@ -2991,8 +2944,8 @@
       <c r="F3" s="17"/>
       <c r="G3" s="17"/>
       <c r="H3" s="17"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="54"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:10">
       <c r="A4" s="18" t="s">
@@ -3020,7 +2973,7 @@
       <c r="I4" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="54"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:10">
       <c r="A5" s="21" t="s">
@@ -3046,111 +2999,55 @@
       <c r="I5" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="54"/>
+      <c r="J5" s="51"/>
     </row>
     <row r="6" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A6" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>38</v>
-      </c>
+      <c r="A6" s="23"/>
+      <c r="B6" s="24"/>
       <c r="C6" s="24"/>
       <c r="D6" s="24"/>
-      <c r="E6" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="18">
-        <v>3</v>
-      </c>
-      <c r="G6" s="25">
-        <v>0.8</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="55" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" s="56"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A7" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>41</v>
-      </c>
+      <c r="A7" s="23"/>
+      <c r="B7" s="26"/>
       <c r="C7" s="24"/>
       <c r="D7" s="24"/>
-      <c r="E7" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="18">
-        <v>6</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="J7" s="56"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="53"/>
     </row>
     <row r="8" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A8" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>44</v>
-      </c>
+      <c r="A8" s="23"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="24"/>
       <c r="D8" s="24"/>
-      <c r="E8" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="18">
-        <v>6</v>
-      </c>
-      <c r="G8" s="25">
-        <v>1</v>
-      </c>
-      <c r="H8" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="J8" s="56"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A9" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>46</v>
-      </c>
+      <c r="A9" s="23"/>
+      <c r="B9" s="26"/>
       <c r="C9" s="24"/>
       <c r="D9" s="24"/>
-      <c r="E9" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="18">
-        <v>2</v>
-      </c>
-      <c r="G9" s="25">
-        <v>1</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="55" t="s">
-        <v>47</v>
-      </c>
-      <c r="J9" s="56"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="53"/>
     </row>
     <row r="10" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A10" s="23"/>
@@ -3162,7 +3059,7 @@
       <c r="G10" s="25"/>
       <c r="H10" s="18"/>
       <c r="I10" s="18"/>
-      <c r="J10" s="56"/>
+      <c r="J10" s="53"/>
     </row>
     <row r="11" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A11" s="23"/>
@@ -3174,7 +3071,7 @@
       <c r="G11" s="25"/>
       <c r="H11" s="18"/>
       <c r="I11" s="18"/>
-      <c r="J11" s="56"/>
+      <c r="J11" s="53"/>
     </row>
     <row r="12" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A12" s="27"/>
@@ -3185,8 +3082,8 @@
       <c r="F12" s="18"/>
       <c r="G12" s="25"/>
       <c r="H12" s="18"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="56"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="53"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A13" s="27"/>
@@ -3198,7 +3095,7 @@
       <c r="G13" s="25"/>
       <c r="H13" s="18"/>
       <c r="I13" s="18"/>
-      <c r="J13" s="56"/>
+      <c r="J13" s="53"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A14" s="27"/>
@@ -3210,7 +3107,7 @@
       <c r="G14" s="25"/>
       <c r="H14" s="18"/>
       <c r="I14" s="18"/>
-      <c r="J14" s="56"/>
+      <c r="J14" s="53"/>
     </row>
     <row r="15" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A15" s="27"/>
@@ -3221,8 +3118,8 @@
       <c r="F15" s="18"/>
       <c r="G15" s="25"/>
       <c r="H15" s="18"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="56"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="53"/>
     </row>
     <row r="16" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A16" s="27"/>
@@ -3234,7 +3131,7 @@
       <c r="G16" s="25"/>
       <c r="H16" s="18"/>
       <c r="I16" s="18"/>
-      <c r="J16" s="56"/>
+      <c r="J16" s="53"/>
     </row>
     <row r="17" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A17" s="27"/>
@@ -3246,7 +3143,7 @@
       <c r="G17" s="25"/>
       <c r="H17" s="18"/>
       <c r="I17" s="18"/>
-      <c r="J17" s="56"/>
+      <c r="J17" s="53"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A18" s="27"/>
@@ -3258,7 +3155,7 @@
       <c r="G18" s="25"/>
       <c r="H18" s="18"/>
       <c r="I18" s="18"/>
-      <c r="J18" s="56"/>
+      <c r="J18" s="53"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A19" s="27"/>
@@ -3270,7 +3167,7 @@
       <c r="G19" s="25"/>
       <c r="H19" s="18"/>
       <c r="I19" s="18"/>
-      <c r="J19" s="56"/>
+      <c r="J19" s="53"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A20" s="31"/>
@@ -3282,7 +3179,7 @@
       <c r="G20" s="25"/>
       <c r="H20" s="18"/>
       <c r="I20" s="18"/>
-      <c r="J20" s="56"/>
+      <c r="J20" s="53"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A21" s="21"/>
@@ -3294,7 +3191,7 @@
       <c r="G21" s="25"/>
       <c r="H21" s="18"/>
       <c r="I21" s="18"/>
-      <c r="J21" s="56"/>
+      <c r="J21" s="53"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A22" s="23"/>
@@ -3306,7 +3203,7 @@
       <c r="G22" s="25"/>
       <c r="H22" s="18"/>
       <c r="I22" s="18"/>
-      <c r="J22" s="56"/>
+      <c r="J22" s="53"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A23" s="21"/>
@@ -3318,7 +3215,7 @@
       <c r="G23" s="25"/>
       <c r="H23" s="18"/>
       <c r="I23" s="18"/>
-      <c r="J23" s="56"/>
+      <c r="J23" s="53"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A24" s="27"/>
@@ -3330,7 +3227,7 @@
       <c r="G24" s="25"/>
       <c r="H24" s="18"/>
       <c r="I24" s="18"/>
-      <c r="J24" s="56"/>
+      <c r="J24" s="53"/>
     </row>
     <row r="25" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A25" s="27"/>
@@ -3342,7 +3239,7 @@
       <c r="G25" s="25"/>
       <c r="H25" s="18"/>
       <c r="I25" s="18"/>
-      <c r="J25" s="56"/>
+      <c r="J25" s="53"/>
     </row>
     <row r="26" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A26" s="23"/>
@@ -3354,7 +3251,7 @@
       <c r="G26" s="25"/>
       <c r="H26" s="18"/>
       <c r="I26" s="18"/>
-      <c r="J26" s="56"/>
+      <c r="J26" s="53"/>
     </row>
     <row r="27" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A27" s="21"/>
@@ -3366,11 +3263,11 @@
       <c r="G27" s="25"/>
       <c r="H27" s="18"/>
       <c r="I27" s="18"/>
-      <c r="J27" s="56"/>
+      <c r="J27" s="53"/>
     </row>
     <row r="28" s="2" customFormat="1" ht="30" customHeight="1" spans="1:10">
       <c r="A28" s="32" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B28" s="33"/>
       <c r="C28" s="33"/>
@@ -3379,16 +3276,12 @@
       <c r="F28" s="33"/>
       <c r="G28" s="33"/>
       <c r="H28" s="33"/>
-      <c r="I28" s="58"/>
-      <c r="J28" s="56"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="53"/>
     </row>
     <row r="29" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A29" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="24" t="s">
-        <v>49</v>
-      </c>
+      <c r="A29" s="23"/>
+      <c r="B29" s="24"/>
       <c r="C29" s="24"/>
       <c r="D29" s="24"/>
       <c r="E29" s="18"/>
@@ -3396,15 +3289,11 @@
       <c r="G29" s="25"/>
       <c r="H29" s="18"/>
       <c r="I29" s="18"/>
-      <c r="J29" s="56"/>
+      <c r="J29" s="53"/>
     </row>
     <row r="30" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A30" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="26" t="s">
-        <v>50</v>
-      </c>
+      <c r="A30" s="23"/>
+      <c r="B30" s="26"/>
       <c r="C30" s="24"/>
       <c r="D30" s="24"/>
       <c r="E30" s="18"/>
@@ -3412,7 +3301,7 @@
       <c r="G30" s="25"/>
       <c r="H30" s="18"/>
       <c r="I30" s="18"/>
-      <c r="J30" s="56"/>
+      <c r="J30" s="53"/>
     </row>
     <row r="31" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A31" s="36"/>
@@ -3424,7 +3313,7 @@
       <c r="G31" s="25"/>
       <c r="H31" s="18"/>
       <c r="I31" s="18"/>
-      <c r="J31" s="56"/>
+      <c r="J31" s="53"/>
     </row>
     <row r="32" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A32" s="34"/>
@@ -3436,7 +3325,7 @@
       <c r="G32" s="25"/>
       <c r="H32" s="18"/>
       <c r="I32" s="18"/>
-      <c r="J32" s="56"/>
+      <c r="J32" s="53"/>
     </row>
     <row r="33" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A33" s="39"/>
@@ -3448,7 +3337,7 @@
       <c r="G33" s="25"/>
       <c r="H33" s="18"/>
       <c r="I33" s="18"/>
-      <c r="J33" s="56"/>
+      <c r="J33" s="53"/>
     </row>
     <row r="34" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A34" s="39"/>
@@ -3460,7 +3349,7 @@
       <c r="G34" s="25"/>
       <c r="H34" s="18"/>
       <c r="I34" s="18"/>
-      <c r="J34" s="56"/>
+      <c r="J34" s="53"/>
     </row>
     <row r="35" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A35" s="40"/>
@@ -3472,7 +3361,7 @@
       <c r="G35" s="25"/>
       <c r="H35" s="18"/>
       <c r="I35" s="18"/>
-      <c r="J35" s="56"/>
+      <c r="J35" s="53"/>
     </row>
     <row r="36" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A36" s="36"/>
@@ -3484,7 +3373,7 @@
       <c r="G36" s="25"/>
       <c r="H36" s="18"/>
       <c r="I36" s="18"/>
-      <c r="J36" s="56"/>
+      <c r="J36" s="53"/>
     </row>
     <row r="37" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A37" s="36"/>
@@ -3496,7 +3385,7 @@
       <c r="G37" s="25"/>
       <c r="H37" s="18"/>
       <c r="I37" s="18"/>
-      <c r="J37" s="56"/>
+      <c r="J37" s="53"/>
     </row>
     <row r="38" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A38" s="36"/>
@@ -3508,19 +3397,19 @@
       <c r="G38" s="25"/>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
-      <c r="J38" s="56"/>
+      <c r="J38" s="53"/>
     </row>
     <row r="39" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A39" s="36"/>
-      <c r="B39" s="41"/>
-      <c r="C39" s="42"/>
-      <c r="D39" s="43"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="30"/>
       <c r="E39" s="18"/>
       <c r="F39" s="38"/>
       <c r="G39" s="25"/>
       <c r="H39" s="18"/>
       <c r="I39" s="18"/>
-      <c r="J39" s="56"/>
+      <c r="J39" s="53"/>
     </row>
     <row r="40" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A40" s="36"/>
@@ -3532,11 +3421,11 @@
       <c r="G40" s="25"/>
       <c r="H40" s="18"/>
       <c r="I40" s="18"/>
-      <c r="J40" s="56"/>
+      <c r="J40" s="53"/>
     </row>
     <row r="41" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
       <c r="A41" s="16" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B41" s="17"/>
       <c r="C41" s="17"/>
@@ -3545,22 +3434,22 @@
       <c r="F41" s="17"/>
       <c r="G41" s="17"/>
       <c r="H41" s="17"/>
-      <c r="I41" s="53"/>
+      <c r="I41" s="50"/>
     </row>
     <row r="42" s="1" customFormat="1" ht="50.1" customHeight="1" spans="1:9">
-      <c r="A42" s="44"/>
-      <c r="B42" s="45"/>
-      <c r="C42" s="45"/>
-      <c r="D42" s="45"/>
-      <c r="E42" s="45"/>
-      <c r="F42" s="45"/>
-      <c r="G42" s="45"/>
-      <c r="H42" s="45"/>
-      <c r="I42" s="59"/>
+      <c r="A42" s="41"/>
+      <c r="B42" s="42"/>
+      <c r="C42" s="42"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="56"/>
     </row>
     <row r="43" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
       <c r="A43" s="32" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B43" s="33"/>
       <c r="C43" s="33"/>
@@ -3569,103 +3458,103 @@
       <c r="F43" s="33"/>
       <c r="G43" s="33"/>
       <c r="H43" s="33"/>
-      <c r="I43" s="58"/>
+      <c r="I43" s="55"/>
     </row>
     <row r="44" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
       <c r="A44" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="B44" s="46"/>
-      <c r="C44" s="47"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="47"/>
-      <c r="G44" s="47"/>
-      <c r="H44" s="47"/>
-      <c r="I44" s="60"/>
+        <v>40</v>
+      </c>
+      <c r="B44" s="43"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="44"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="44"/>
+      <c r="I44" s="57"/>
     </row>
     <row r="45" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
       <c r="A45" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="B45" s="46"/>
-      <c r="C45" s="47"/>
-      <c r="D45" s="47"/>
-      <c r="E45" s="47"/>
-      <c r="F45" s="47"/>
-      <c r="G45" s="47"/>
-      <c r="H45" s="47"/>
-      <c r="I45" s="60"/>
+        <v>41</v>
+      </c>
+      <c r="B45" s="43"/>
+      <c r="C45" s="44"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="44"/>
+      <c r="F45" s="44"/>
+      <c r="G45" s="44"/>
+      <c r="H45" s="44"/>
+      <c r="I45" s="57"/>
     </row>
     <row r="46" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
       <c r="A46" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="B46" s="46"/>
-      <c r="C46" s="47"/>
-      <c r="D46" s="47"/>
-      <c r="E46" s="47"/>
-      <c r="F46" s="47"/>
-      <c r="G46" s="47"/>
-      <c r="H46" s="47"/>
-      <c r="I46" s="60"/>
+        <v>42</v>
+      </c>
+      <c r="B46" s="43"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="44"/>
+      <c r="F46" s="44"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="44"/>
+      <c r="I46" s="57"/>
     </row>
     <row r="47" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A47" s="48" t="s">
-        <v>56</v>
-      </c>
-      <c r="B47" s="48"/>
-      <c r="C47" s="48"/>
-      <c r="D47" s="48"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="48"/>
-      <c r="G47" s="48"/>
-      <c r="H47" s="48"/>
-      <c r="I47" s="61"/>
+      <c r="A47" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="B47" s="45"/>
+      <c r="C47" s="45"/>
+      <c r="D47" s="45"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="45"/>
+      <c r="G47" s="45"/>
+      <c r="H47" s="45"/>
+      <c r="I47" s="58"/>
     </row>
     <row r="48" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A48" s="49"/>
-      <c r="B48" s="49"/>
-      <c r="C48" s="49"/>
-      <c r="D48" s="49"/>
-      <c r="E48" s="49"/>
-      <c r="F48" s="49"/>
-      <c r="G48" s="49"/>
-      <c r="H48" s="49"/>
-      <c r="I48" s="62"/>
+      <c r="A48" s="46"/>
+      <c r="B48" s="46"/>
+      <c r="C48" s="46"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="46"/>
+      <c r="F48" s="46"/>
+      <c r="G48" s="46"/>
+      <c r="H48" s="46"/>
+      <c r="I48" s="59"/>
     </row>
     <row r="49" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A49" s="49"/>
-      <c r="B49" s="49"/>
-      <c r="C49" s="49"/>
-      <c r="D49" s="49"/>
-      <c r="E49" s="49"/>
-      <c r="F49" s="49"/>
-      <c r="G49" s="49"/>
-      <c r="H49" s="49"/>
-      <c r="I49" s="62"/>
+      <c r="A49" s="46"/>
+      <c r="B49" s="46"/>
+      <c r="C49" s="46"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="46"/>
+      <c r="G49" s="46"/>
+      <c r="H49" s="46"/>
+      <c r="I49" s="59"/>
     </row>
     <row r="50" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A50" s="49"/>
-      <c r="B50" s="49"/>
-      <c r="C50" s="49"/>
-      <c r="D50" s="49"/>
-      <c r="E50" s="49"/>
-      <c r="F50" s="49"/>
-      <c r="G50" s="49"/>
-      <c r="H50" s="49"/>
-      <c r="I50" s="62"/>
+      <c r="A50" s="46"/>
+      <c r="B50" s="46"/>
+      <c r="C50" s="46"/>
+      <c r="D50" s="46"/>
+      <c r="E50" s="46"/>
+      <c r="F50" s="46"/>
+      <c r="G50" s="46"/>
+      <c r="H50" s="46"/>
+      <c r="I50" s="59"/>
     </row>
     <row r="51" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A51" s="50"/>
-      <c r="B51" s="51"/>
-      <c r="C51" s="51"/>
-      <c r="D51" s="51"/>
-      <c r="E51" s="51"/>
-      <c r="F51" s="51"/>
-      <c r="G51" s="51"/>
-      <c r="H51" s="51"/>
-      <c r="I51" s="63"/>
+      <c r="A51" s="47"/>
+      <c r="B51" s="48"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="48"/>
+      <c r="E51" s="48"/>
+      <c r="F51" s="48"/>
+      <c r="G51" s="48"/>
+      <c r="H51" s="48"/>
+      <c r="I51" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="52">

--- a/src/main/resources/template2.xlsx
+++ b/src/main/resources/template2.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25726"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RedMiG\IdeaProjects\CreateWrodEscel\src\main\resources\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A330F7F8-1636-4F79-9A1B-0B7DE461AA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25395" windowHeight="11385" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="附注" sheetId="1" r:id="rId1"/>
@@ -15,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t xml:space="preserve">                                                                                                                                                          </t>
   </si>
@@ -175,7 +181,7 @@
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>4</t>
     </r>
@@ -185,7 +191,7 @@
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>.</t>
     </r>
@@ -215,7 +221,7 @@
         <sz val="10.5"/>
         <color indexed="8"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>5</t>
     </r>
@@ -225,7 +231,7 @@
         <sz val="10.5"/>
         <color indexed="8"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>.</t>
     </r>
@@ -255,7 +261,7 @@
         <sz val="10.5"/>
         <color indexed="8"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>6</t>
     </r>
@@ -265,7 +271,7 @@
         <sz val="10.5"/>
         <color indexed="8"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>.</t>
     </r>
@@ -304,7 +310,7 @@
         <sz val="10.5"/>
         <color indexed="8"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>7</t>
     </r>
@@ -314,7 +320,7 @@
         <sz val="10.5"/>
         <color indexed="8"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>.</t>
     </r>
@@ -353,7 +359,7 @@
         <sz val="10.5"/>
         <color indexed="8"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>8</t>
     </r>
@@ -363,7 +369,7 @@
         <sz val="10.5"/>
         <color indexed="8"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>.</t>
     </r>
@@ -393,7 +399,7 @@
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>9</t>
     </r>
@@ -403,7 +409,7 @@
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>.</t>
     </r>
@@ -432,7 +438,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>10</t>
     </r>
@@ -441,7 +447,7 @@
         <b/>
         <sz val="10.5"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>.</t>
     </r>
@@ -467,7 +473,7 @@
         <b/>
         <sz val="10.5"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>/</t>
     </r>
@@ -502,7 +508,7 @@
         <b/>
         <sz val="10.5"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>/</t>
     </r>
@@ -547,7 +553,7 @@
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>11</t>
     </r>
@@ -557,7 +563,7 @@
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>.</t>
     </r>
@@ -652,7 +658,7 @@
         <sz val="10.5"/>
         <color indexed="8"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>12</t>
     </r>
@@ -662,7 +668,7 @@
         <sz val="10.5"/>
         <color indexed="8"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>.</t>
     </r>
@@ -761,7 +767,7 @@
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>15</t>
     </r>
@@ -771,7 +777,7 @@
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>.</t>
     </r>
@@ -800,7 +806,7 @@
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>XX</t>
     </r>
@@ -820,7 +826,7 @@
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>XX</t>
     </r>
@@ -840,7 +846,7 @@
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>XX</t>
     </r>
@@ -860,7 +866,7 @@
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>XX</t>
     </r>
@@ -880,7 +886,7 @@
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>-XX</t>
     </r>
@@ -900,7 +906,7 @@
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>-XX</t>
     </r>
@@ -929,7 +935,7 @@
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>2018</t>
     </r>
@@ -949,7 +955,7 @@
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>1</t>
     </r>
@@ -969,7 +975,7 @@
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>19</t>
     </r>
@@ -989,7 +995,7 @@
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>-</t>
     </r>
@@ -1009,7 +1015,7 @@
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>-</t>
     </r>
@@ -1058,9 +1064,6 @@
     <t>计划人</t>
   </si>
   <si>
-    <t>侯文康</t>
-  </si>
-  <si>
     <t>计划日期</t>
   </si>
   <si>
@@ -1113,19 +1116,16 @@
   </si>
   <si>
     <t>工作中的不足和需改进之处</t>
+  </si>
+  <si>
+    <t>你的姓名</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="42">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -1196,176 +1196,25 @@
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color indexed="8"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10.5"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -1385,13 +1234,13 @@
       <sz val="10.5"/>
       <color indexed="8"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10.5"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -1417,8 +1266,19 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1437,194 +1297,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="24">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1815,258 +1489,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2074,13 +1506,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2088,7 +1514,67 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2100,6 +1586,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2112,56 +1601,38 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2169,37 +1640,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2214,154 +1670,32 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="普通 2" xfId="13"/>
-    <cellStyle name="注释" xfId="14" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="15" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="16" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="17" builtinId="11"/>
-    <cellStyle name="标题" xfId="18" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="19" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="20" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="21" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="22" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="23" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="24" builtinId="44"/>
-    <cellStyle name="输出" xfId="25" builtinId="21"/>
-    <cellStyle name="计算" xfId="26" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="27" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="28" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="30" builtinId="24"/>
-    <cellStyle name="汇总" xfId="31" builtinId="25"/>
-    <cellStyle name="好" xfId="32" builtinId="26"/>
-    <cellStyle name="适中" xfId="33" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="34" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="35" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="36" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="37" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="38" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="39" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="40" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="41" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="42" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="43" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="44" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="45" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="46" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="47" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="48" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="49" builtinId="52"/>
+    <cellStyle name="普通 2" xfId="1" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <colors>
     <mruColors>
-      <color rgb="00FFFF00"/>
-      <color rgb="000000FF"/>
+      <color rgb="FFFFFF00"/>
+      <color rgb="FF0000FF"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2377,13 +1711,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1" descr="智盾logo"/>
+        <xdr:cNvPr id="2" name="图片 1" descr="智盾logo">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2404,7 +1744,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2420,13 +1760,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1" descr="智盾logo"/>
+        <xdr:cNvPr id="2" name="图片 1" descr="智盾logo">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2774,846 +2120,797 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr/>
-  <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:A19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="205.375" customWidth="1"/>
+    <col min="1" max="1" width="205.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36.75" customHeight="1" spans="1:7">
-      <c r="A1" s="61" t="s">
+    <row r="1" spans="1:1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-    </row>
-    <row r="2" ht="33" customHeight="1" spans="1:1">
-      <c r="A2" s="63" t="s">
+    </row>
+    <row r="2" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="33" customHeight="1" spans="1:1">
-      <c r="A3" s="64" t="s">
+    <row r="3" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="33" customHeight="1" spans="1:1">
-      <c r="A4" s="63" t="s">
+    <row r="4" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="33" customHeight="1" spans="1:1">
-      <c r="A5" s="64" t="s">
+    <row r="5" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" ht="33" customHeight="1" spans="1:1">
-      <c r="A6" s="65" t="s">
+    <row r="6" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" ht="33" customHeight="1" spans="1:1">
-      <c r="A7" s="66" t="s">
+    <row r="7" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" ht="33" customHeight="1" spans="1:1">
-      <c r="A8" s="66" t="s">
+    <row r="8" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" ht="33" customHeight="1" spans="1:1">
-      <c r="A9" s="66" t="s">
+    <row r="9" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" ht="33" customHeight="1" spans="1:1">
-      <c r="A10" s="66" t="s">
+    <row r="10" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" ht="33" customHeight="1" spans="1:1">
-      <c r="A11" s="65" t="s">
+    <row r="11" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" ht="33" customHeight="1" spans="1:1">
-      <c r="A12" s="67" t="s">
+    <row r="12" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" ht="33" customHeight="1" spans="1:1">
-      <c r="A13" s="68" t="s">
+    <row r="13" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="20" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" ht="33" customHeight="1" spans="1:1">
-      <c r="A14" s="66" t="s">
+    <row r="14" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" ht="33" customHeight="1" spans="1:1">
-      <c r="A15" s="69" t="s">
+    <row r="15" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" ht="33" customHeight="1" spans="1:1">
-      <c r="A16" s="70" t="s">
+    <row r="16" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" ht="33" customHeight="1" spans="1:1">
-      <c r="A17" s="71" t="s">
+    <row r="17" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="23" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" ht="33" customHeight="1" spans="1:1">
-      <c r="A18" s="72" t="s">
+    <row r="18" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="24" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" ht="33" customHeight="1" spans="1:1">
-      <c r="A19" s="73" t="s">
+    <row r="19" spans="1:1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="25" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="74"/>
-    </row>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="23" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr/>
-  <dimension ref="A1:J51"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I51"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.2916666666667" style="3" customWidth="1"/>
-    <col min="2" max="2" width="17.5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="10.375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="39.75" style="3" customWidth="1"/>
-    <col min="5" max="5" width="8.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.875" style="4" customWidth="1"/>
-    <col min="9" max="9" width="74.5" style="5" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="20.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="39.77734375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="74.44140625" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="39" customHeight="1" spans="1:4">
-      <c r="A1" s="6"/>
-      <c r="B1" s="7"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="9"/>
-    </row>
-    <row r="2" ht="23" customHeight="1" spans="1:9">
-      <c r="A2" s="10" t="s">
+    <row r="1" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="27"/>
+    </row>
+    <row r="2" spans="1:9" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="15" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="49"/>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:10">
-      <c r="A3" s="16" t="s">
+      <c r="I2" s="33"/>
+    </row>
+    <row r="3" spans="1:9" s="1" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="51"/>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:10">
-      <c r="A4" s="18" t="s">
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="37"/>
+    </row>
+    <row r="4" spans="1:9" s="1" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="F4" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="G4" s="39"/>
+      <c r="H4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="20"/>
-      <c r="H4" s="18" t="s">
+      <c r="I4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="18" t="s">
+    </row>
+    <row r="5" spans="1:9" s="1" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="51"/>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:10">
-      <c r="A5" s="21" t="s">
+      <c r="B5" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="C5" s="40"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="18" t="s">
+      <c r="F5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="G5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="H5" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="I5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I5" s="18" t="s">
+    </row>
+    <row r="6" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="12"/>
+    </row>
+    <row r="7" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="12"/>
+    </row>
+    <row r="10" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+    </row>
+    <row r="12" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="13"/>
+    </row>
+    <row r="13" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+    </row>
+    <row r="14" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="9"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+    </row>
+    <row r="15" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="9"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="13"/>
+    </row>
+    <row r="16" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+    </row>
+    <row r="17" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="9"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+    </row>
+    <row r="18" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="9"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+    </row>
+    <row r="19" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+    </row>
+    <row r="20" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="10"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+    </row>
+    <row r="21" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+    </row>
+    <row r="22" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+    </row>
+    <row r="23" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="6"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+    </row>
+    <row r="24" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="9"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+    </row>
+    <row r="25" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="9"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+    </row>
+    <row r="26" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+    </row>
+    <row r="27" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="6"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+    </row>
+    <row r="28" spans="1:9" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="51"/>
-    </row>
-    <row r="6" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A6" s="23"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="53"/>
-    </row>
-    <row r="7" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A7" s="23"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="53"/>
-    </row>
-    <row r="8" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A8" s="23"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="53"/>
-    </row>
-    <row r="9" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A9" s="23"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="53"/>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A10" s="23"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="53"/>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A11" s="23"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="53"/>
-    </row>
-    <row r="12" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A12" s="27"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="53"/>
-    </row>
-    <row r="13" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A13" s="27"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="53"/>
-    </row>
-    <row r="14" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A14" s="27"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="53"/>
-    </row>
-    <row r="15" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A15" s="27"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="53"/>
-    </row>
-    <row r="16" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A16" s="27"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="53"/>
-    </row>
-    <row r="17" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A17" s="27"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="53"/>
-    </row>
-    <row r="18" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A18" s="27"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="53"/>
-    </row>
-    <row r="19" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A19" s="27"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="53"/>
-    </row>
-    <row r="20" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A20" s="31"/>
-      <c r="B20" s="26"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="53"/>
-    </row>
-    <row r="21" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A21" s="21"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="53"/>
-    </row>
-    <row r="22" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A22" s="23"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="53"/>
-    </row>
-    <row r="23" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A23" s="21"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="53"/>
-    </row>
-    <row r="24" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A24" s="27"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="53"/>
-    </row>
-    <row r="25" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A25" s="27"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="53"/>
-    </row>
-    <row r="26" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A26" s="23"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="53"/>
-    </row>
-    <row r="27" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A27" s="21"/>
-      <c r="B27" s="26"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="53"/>
-    </row>
-    <row r="28" s="2" customFormat="1" ht="30" customHeight="1" spans="1:10">
-      <c r="A28" s="32" t="s">
+      <c r="B28" s="46"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="46"/>
+    </row>
+    <row r="29" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+    </row>
+    <row r="30" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+    </row>
+    <row r="31" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="10"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+    </row>
+    <row r="32" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="42"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+    </row>
+    <row r="33" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="9"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+    </row>
+    <row r="34" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="9"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+    </row>
+    <row r="35" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="7"/>
+      <c r="B35" s="41"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+    </row>
+    <row r="36" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="10"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+    </row>
+    <row r="37" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="10"/>
+      <c r="B37" s="41"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+    </row>
+    <row r="38" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="10"/>
+      <c r="B38" s="41"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+    </row>
+    <row r="39" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="10"/>
+      <c r="B39" s="42"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+    </row>
+    <row r="40" spans="1:9" s="1" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="10"/>
+      <c r="B40" s="41"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+    </row>
+    <row r="41" spans="1:9" s="1" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="33"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="53"/>
-    </row>
-    <row r="29" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A29" s="23"/>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="53"/>
-    </row>
-    <row r="30" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A30" s="23"/>
-      <c r="B30" s="26"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="53"/>
-    </row>
-    <row r="31" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A31" s="36"/>
-      <c r="B31" s="26"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="53"/>
-    </row>
-    <row r="32" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A32" s="34"/>
-      <c r="B32" s="37"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="53"/>
-    </row>
-    <row r="33" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A33" s="39"/>
-      <c r="B33" s="26"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="53"/>
-    </row>
-    <row r="34" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A34" s="39"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="53"/>
-    </row>
-    <row r="35" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A35" s="40"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="38"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="53"/>
-    </row>
-    <row r="36" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A36" s="36"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="53"/>
-    </row>
-    <row r="37" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A37" s="36"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="53"/>
-    </row>
-    <row r="38" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A38" s="36"/>
-      <c r="B38" s="26"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="53"/>
-    </row>
-    <row r="39" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A39" s="36"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="29"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="38"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="53"/>
-    </row>
-    <row r="40" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
-      <c r="A40" s="36"/>
-      <c r="B40" s="26"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
-      <c r="J40" s="53"/>
-    </row>
-    <row r="41" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A41" s="16" t="s">
+      <c r="B41" s="36"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="36"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="37"/>
+    </row>
+    <row r="42" spans="1:9" s="1" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="47"/>
+      <c r="B42" s="48"/>
+      <c r="C42" s="48"/>
+      <c r="D42" s="48"/>
+      <c r="E42" s="48"/>
+      <c r="F42" s="48"/>
+      <c r="G42" s="48"/>
+      <c r="H42" s="48"/>
+      <c r="I42" s="49"/>
+    </row>
+    <row r="43" spans="1:9" s="1" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="50"/>
-    </row>
-    <row r="42" s="1" customFormat="1" ht="50.1" customHeight="1" spans="1:9">
-      <c r="A42" s="41"/>
-      <c r="B42" s="42"/>
-      <c r="C42" s="42"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="56"/>
-    </row>
-    <row r="43" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A43" s="32" t="s">
+      <c r="B43" s="46"/>
+      <c r="C43" s="46"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="46"/>
+      <c r="F43" s="46"/>
+      <c r="G43" s="46"/>
+      <c r="H43" s="46"/>
+      <c r="I43" s="46"/>
+    </row>
+    <row r="44" spans="1:9" s="1" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="33"/>
-      <c r="C43" s="33"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="33"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="55"/>
-    </row>
-    <row r="44" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A44" s="38" t="s">
+      <c r="B44" s="50"/>
+      <c r="C44" s="51"/>
+      <c r="D44" s="51"/>
+      <c r="E44" s="51"/>
+      <c r="F44" s="51"/>
+      <c r="G44" s="51"/>
+      <c r="H44" s="51"/>
+      <c r="I44" s="52"/>
+    </row>
+    <row r="45" spans="1:9" s="1" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="43"/>
-      <c r="C44" s="44"/>
-      <c r="D44" s="44"/>
-      <c r="E44" s="44"/>
-      <c r="F44" s="44"/>
-      <c r="G44" s="44"/>
-      <c r="H44" s="44"/>
-      <c r="I44" s="57"/>
-    </row>
-    <row r="45" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A45" s="38" t="s">
+      <c r="B45" s="50"/>
+      <c r="C45" s="51"/>
+      <c r="D45" s="51"/>
+      <c r="E45" s="51"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="51"/>
+      <c r="H45" s="51"/>
+      <c r="I45" s="52"/>
+    </row>
+    <row r="46" spans="1:9" s="1" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B45" s="43"/>
-      <c r="C45" s="44"/>
-      <c r="D45" s="44"/>
-      <c r="E45" s="44"/>
-      <c r="F45" s="44"/>
-      <c r="G45" s="44"/>
-      <c r="H45" s="44"/>
-      <c r="I45" s="57"/>
-    </row>
-    <row r="46" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A46" s="38" t="s">
+      <c r="B46" s="50"/>
+      <c r="C46" s="51"/>
+      <c r="D46" s="51"/>
+      <c r="E46" s="51"/>
+      <c r="F46" s="51"/>
+      <c r="G46" s="51"/>
+      <c r="H46" s="51"/>
+      <c r="I46" s="52"/>
+    </row>
+    <row r="47" spans="1:9" s="1" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="B46" s="43"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="44"/>
-      <c r="E46" s="44"/>
-      <c r="F46" s="44"/>
-      <c r="G46" s="44"/>
-      <c r="H46" s="44"/>
-      <c r="I46" s="57"/>
-    </row>
-    <row r="47" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A47" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="B47" s="45"/>
-      <c r="C47" s="45"/>
-      <c r="D47" s="45"/>
-      <c r="E47" s="45"/>
-      <c r="F47" s="45"/>
-      <c r="G47" s="45"/>
-      <c r="H47" s="45"/>
-      <c r="I47" s="58"/>
-    </row>
-    <row r="48" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A48" s="46"/>
-      <c r="B48" s="46"/>
-      <c r="C48" s="46"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="46"/>
-      <c r="F48" s="46"/>
-      <c r="G48" s="46"/>
-      <c r="H48" s="46"/>
-      <c r="I48" s="59"/>
-    </row>
-    <row r="49" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A49" s="46"/>
-      <c r="B49" s="46"/>
-      <c r="C49" s="46"/>
-      <c r="D49" s="46"/>
-      <c r="E49" s="46"/>
-      <c r="F49" s="46"/>
-      <c r="G49" s="46"/>
-      <c r="H49" s="46"/>
-      <c r="I49" s="59"/>
-    </row>
-    <row r="50" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A50" s="46"/>
-      <c r="B50" s="46"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="46"/>
-      <c r="E50" s="46"/>
-      <c r="F50" s="46"/>
-      <c r="G50" s="46"/>
-      <c r="H50" s="46"/>
-      <c r="I50" s="59"/>
-    </row>
-    <row r="51" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:9">
-      <c r="A51" s="47"/>
-      <c r="B51" s="48"/>
-      <c r="C51" s="48"/>
-      <c r="D51" s="48"/>
-      <c r="E51" s="48"/>
-      <c r="F51" s="48"/>
-      <c r="G51" s="48"/>
-      <c r="H51" s="48"/>
-      <c r="I51" s="60"/>
+      <c r="B47" s="53"/>
+      <c r="C47" s="53"/>
+      <c r="D47" s="53"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="53"/>
+      <c r="G47" s="53"/>
+      <c r="H47" s="53"/>
+      <c r="I47" s="53"/>
+    </row>
+    <row r="48" spans="1:9" s="1" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="54"/>
+      <c r="B48" s="54"/>
+      <c r="C48" s="54"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="54"/>
+    </row>
+    <row r="49" spans="1:9" s="1" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="54"/>
+      <c r="B49" s="54"/>
+      <c r="C49" s="54"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="54"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="54"/>
+      <c r="I49" s="54"/>
+    </row>
+    <row r="50" spans="1:9" s="1" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="54"/>
+      <c r="B50" s="54"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="54"/>
+    </row>
+    <row r="51" spans="1:9" s="1" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="55"/>
+      <c r="B51" s="56"/>
+      <c r="C51" s="56"/>
+      <c r="D51" s="56"/>
+      <c r="E51" s="56"/>
+      <c r="F51" s="56"/>
+      <c r="G51" s="56"/>
+      <c r="H51" s="56"/>
+      <c r="I51" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="A42:I42"/>
-    <mergeCell ref="A43:I43"/>
-    <mergeCell ref="B44:I44"/>
-    <mergeCell ref="B45:I45"/>
-    <mergeCell ref="B46:I46"/>
-    <mergeCell ref="A47:I47"/>
-    <mergeCell ref="A48:I48"/>
-    <mergeCell ref="A49:I49"/>
-    <mergeCell ref="A50:I50"/>
-    <mergeCell ref="A51:I51"/>
   </mergeCells>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.338888888888889" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="23" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.33888888888888902" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="300"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>